--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-01.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-01.xlsx
@@ -22275,7 +22275,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E66" t="n">
